--- a/hpi_scraper/Firmographic/coresignal/coresignal_data.xlsx
+++ b/hpi_scraper/Firmographic/coresignal/coresignal_data.xlsx
@@ -445,14 +445,14 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
@@ -536,60 +536,56 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications Limited</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/company/singtel</t>
+          <t>https://sg.linkedin.com/company/seagrp</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>10534059382 USD</t>
+          <t>19379298000 USD</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Technology, Information and Internet</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>telecommunications | internet | computer networking | wireless technology | it &amp; services | satellite services | digital | mobile infotainment | after-sales service | enterprise solutions | r&amp;d | cyber security | internet of things | digital marketing | cloud computing | smart cities | communications infrastructure | enterprise applications | mobile | communications | appliances | broadband | connectivity | distribution | ecommerce | wearables | fixed | communications group | data</t>
+          <t>technology | digital content | ecommerce | payments | consumer internet | financial services | digital entertainment | digital payments | e-commerce | games | mobile-app | social-networks | sport | messaging | mobile | NAICS: 51 | 518 | SIC: 73 | 737</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>10 Eunos Road 8; Singapore Post Centre #07-31; Singapore, 408600, SG</t>
+          <t>1 Fusionopolis Pl; #17-01; Singapore, Singapore 138522, SG</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>1879</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Public</t>
@@ -597,7 +593,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>1683491606 USD</t>
+          <t>9531000000 USD</t>
         </is>
       </c>
     </row>
